--- a/data/stocks_20260414_111618.xlsx
+++ b/data/stocks_20260414_111618.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="股票池" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W70"/>
+  <dimension ref="A1:W57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1119,69 +1119,69 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>688041</v>
+        <v>300502</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>248.78</v>
+        <v>520</v>
       </c>
       <c r="D10" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="E10" t="n">
-        <v>236.27</v>
+        <v>509.34</v>
       </c>
       <c r="F10" t="n">
-        <v>225.62</v>
+        <v>481.17</v>
       </c>
       <c r="G10" t="n">
-        <v>222.34</v>
+        <v>465.84</v>
       </c>
       <c r="H10" t="n">
-        <v>0.105</v>
+        <v>26.253</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.378</v>
+        <v>20.889</v>
       </c>
       <c r="J10" t="n">
-        <v>74.59999999999999</v>
+        <v>79.37</v>
       </c>
       <c r="K10" t="n">
-        <v>66.26000000000001</v>
+        <v>71.98</v>
       </c>
       <c r="L10" t="n">
-        <v>91.26000000000001</v>
+        <v>94.16</v>
       </c>
       <c r="M10" t="n">
-        <v>80.95999999999999</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>65.44</v>
+        <v>66.53</v>
       </c>
       <c r="O10" t="n">
-        <v>56.54</v>
+        <v>61.94</v>
       </c>
       <c r="P10" t="n">
-        <v>2772.76</v>
+        <v>3877.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>2076.17</v>
+        <v>3976.9</v>
       </c>
       <c r="R10" t="n">
-        <v>1.34</v>
+        <v>0.97</v>
       </c>
       <c r="S10" t="n">
-        <v>251.01</v>
+        <v>522.9400000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>252.86</v>
+        <v>538.9</v>
       </c>
       <c r="U10" t="n">
-        <v>245.03</v>
+        <v>515</v>
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
@@ -1192,69 +1192,69 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>300502</v>
+        <v>300394</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>520</v>
+        <v>345.84</v>
       </c>
       <c r="D11" t="n">
-        <v>1.42</v>
+        <v>-1.47</v>
       </c>
       <c r="E11" t="n">
-        <v>509.34</v>
+        <v>347.93</v>
       </c>
       <c r="F11" t="n">
-        <v>481.17</v>
+        <v>334.86</v>
       </c>
       <c r="G11" t="n">
-        <v>465.84</v>
+        <v>321.33</v>
       </c>
       <c r="H11" t="n">
-        <v>26.253</v>
+        <v>11.687</v>
       </c>
       <c r="I11" t="n">
-        <v>20.889</v>
+        <v>9.382999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>79.37</v>
+        <v>73.23999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>71.98</v>
+        <v>72.81</v>
       </c>
       <c r="L11" t="n">
-        <v>94.16</v>
+        <v>74.09</v>
       </c>
       <c r="M11" t="n">
-        <v>70.93000000000001</v>
+        <v>58</v>
       </c>
       <c r="N11" t="n">
-        <v>66.53</v>
+        <v>57.24</v>
       </c>
       <c r="O11" t="n">
-        <v>61.94</v>
+        <v>57.18</v>
       </c>
       <c r="P11" t="n">
-        <v>3877.38</v>
+        <v>4477.87</v>
       </c>
       <c r="Q11" t="n">
-        <v>3976.9</v>
+        <v>3740.57</v>
       </c>
       <c r="R11" t="n">
-        <v>0.97</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
-        <v>522.9400000000001</v>
+        <v>352.3</v>
       </c>
       <c r="T11" t="n">
-        <v>538.9</v>
+        <v>363</v>
       </c>
       <c r="U11" t="n">
-        <v>515</v>
+        <v>343.8</v>
       </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
@@ -1265,69 +1265,69 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>300394</v>
+        <v>988</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>345.84</v>
+        <v>120.63</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.47</v>
+        <v>-3.62</v>
       </c>
       <c r="E12" t="n">
-        <v>347.93</v>
+        <v>117.41</v>
       </c>
       <c r="F12" t="n">
-        <v>334.86</v>
+        <v>110.34</v>
       </c>
       <c r="G12" t="n">
-        <v>321.33</v>
+        <v>111.41</v>
       </c>
       <c r="H12" t="n">
-        <v>11.687</v>
+        <v>3.85</v>
       </c>
       <c r="I12" t="n">
-        <v>9.382999999999999</v>
+        <v>3.152</v>
       </c>
       <c r="J12" t="n">
-        <v>73.23999999999999</v>
+        <v>79.33</v>
       </c>
       <c r="K12" t="n">
-        <v>72.81</v>
+        <v>64.14</v>
       </c>
       <c r="L12" t="n">
-        <v>74.09</v>
+        <v>109.69</v>
       </c>
       <c r="M12" t="n">
-        <v>58</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>57.24</v>
+        <v>60.99</v>
       </c>
       <c r="O12" t="n">
-        <v>57.18</v>
+        <v>59.89</v>
       </c>
       <c r="P12" t="n">
-        <v>4477.87</v>
+        <v>14122.44</v>
       </c>
       <c r="Q12" t="n">
-        <v>3740.57</v>
+        <v>9726.639999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="S12" t="n">
-        <v>352.3</v>
+        <v>120</v>
       </c>
       <c r="T12" t="n">
-        <v>363</v>
+        <v>124.34</v>
       </c>
       <c r="U12" t="n">
-        <v>343.8</v>
+        <v>118</v>
       </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
@@ -1338,69 +1338,69 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>988</v>
+        <v>603986</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>兆易创新</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>120.63</v>
+        <v>280.01</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.62</v>
+        <v>6.82</v>
       </c>
       <c r="E13" t="n">
-        <v>117.41</v>
+        <v>262.74</v>
       </c>
       <c r="F13" t="n">
-        <v>110.34</v>
+        <v>255.25</v>
       </c>
       <c r="G13" t="n">
-        <v>111.41</v>
+        <v>267.78</v>
       </c>
       <c r="H13" t="n">
-        <v>3.85</v>
+        <v>-5.658</v>
       </c>
       <c r="I13" t="n">
-        <v>3.152</v>
+        <v>-7.701</v>
       </c>
       <c r="J13" t="n">
-        <v>79.33</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>64.14</v>
+        <v>57.88</v>
       </c>
       <c r="L13" t="n">
-        <v>109.69</v>
+        <v>110.43</v>
       </c>
       <c r="M13" t="n">
-        <v>65.73999999999999</v>
+        <v>69.08</v>
       </c>
       <c r="N13" t="n">
-        <v>60.99</v>
+        <v>56.37</v>
       </c>
       <c r="O13" t="n">
-        <v>59.89</v>
+        <v>52.44</v>
       </c>
       <c r="P13" t="n">
-        <v>14122.44</v>
+        <v>4662.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>9726.639999999999</v>
+        <v>3634.58</v>
       </c>
       <c r="R13" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="S13" t="n">
-        <v>120</v>
+        <v>269.5</v>
       </c>
       <c r="T13" t="n">
-        <v>124.34</v>
+        <v>281.23</v>
       </c>
       <c r="U13" t="n">
-        <v>118</v>
+        <v>266.39</v>
       </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
@@ -1411,69 +1411,69 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>603986</v>
+        <v>300042</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>兆易创新</t>
+          <t>朗科科技</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>280.01</v>
+        <v>51.8</v>
       </c>
       <c r="D14" t="n">
-        <v>6.82</v>
+        <v>4.23</v>
       </c>
       <c r="E14" t="n">
-        <v>262.74</v>
+        <v>48.64</v>
       </c>
       <c r="F14" t="n">
-        <v>255.25</v>
+        <v>45.38</v>
       </c>
       <c r="G14" t="n">
-        <v>267.78</v>
+        <v>47.59</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.658</v>
+        <v>2.131</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.701</v>
+        <v>1.931</v>
       </c>
       <c r="J14" t="n">
-        <v>75.40000000000001</v>
+        <v>82.48</v>
       </c>
       <c r="K14" t="n">
-        <v>57.88</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>110.43</v>
+        <v>119.36</v>
       </c>
       <c r="M14" t="n">
-        <v>69.08</v>
+        <v>75.12</v>
       </c>
       <c r="N14" t="n">
-        <v>56.37</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>52.44</v>
+        <v>62.26</v>
       </c>
       <c r="P14" t="n">
-        <v>4662.05</v>
+        <v>3952.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>3634.58</v>
+        <v>3421.06</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="S14" t="n">
-        <v>269.5</v>
+        <v>50.8</v>
       </c>
       <c r="T14" t="n">
-        <v>281.23</v>
+        <v>52.33</v>
       </c>
       <c r="U14" t="n">
-        <v>266.39</v>
+        <v>49.71</v>
       </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
@@ -1484,69 +1484,69 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>688525</v>
+        <v>300302</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>佰维存储</t>
+          <t>同有科技</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>288.1</v>
+        <v>23.45</v>
       </c>
       <c r="D15" t="n">
-        <v>12.61</v>
+        <v>3.08</v>
       </c>
       <c r="E15" t="n">
-        <v>248.53</v>
+        <v>22.35</v>
       </c>
       <c r="F15" t="n">
-        <v>230.88</v>
+        <v>20.96</v>
       </c>
       <c r="G15" t="n">
-        <v>235.2</v>
+        <v>21.85</v>
       </c>
       <c r="H15" t="n">
-        <v>13.638</v>
+        <v>0.447</v>
       </c>
       <c r="I15" t="n">
-        <v>10.623</v>
+        <v>0.257</v>
       </c>
       <c r="J15" t="n">
-        <v>75.34999999999999</v>
+        <v>79.97</v>
       </c>
       <c r="K15" t="n">
-        <v>56.36</v>
+        <v>60.39</v>
       </c>
       <c r="L15" t="n">
-        <v>113.33</v>
+        <v>119.12</v>
       </c>
       <c r="M15" t="n">
-        <v>85.48</v>
+        <v>74.22</v>
       </c>
       <c r="N15" t="n">
-        <v>73.75</v>
+        <v>62.82</v>
       </c>
       <c r="O15" t="n">
-        <v>67.95999999999999</v>
+        <v>58.38</v>
       </c>
       <c r="P15" t="n">
-        <v>5220.18</v>
+        <v>3343.64</v>
       </c>
       <c r="Q15" t="n">
-        <v>3890.53</v>
+        <v>4731.27</v>
       </c>
       <c r="R15" t="n">
-        <v>1.34</v>
+        <v>0.71</v>
       </c>
       <c r="S15" t="n">
-        <v>265.99</v>
+        <v>23.2</v>
       </c>
       <c r="T15" t="n">
-        <v>294.22</v>
+        <v>23.58</v>
       </c>
       <c r="U15" t="n">
-        <v>262.01</v>
+        <v>23</v>
       </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
@@ -1557,69 +1557,69 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>300042</v>
+        <v>20</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>朗科科技</t>
+          <t>深华发A</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>51.8</v>
+        <v>16.03</v>
       </c>
       <c r="D16" t="n">
-        <v>4.23</v>
+        <v>1.2</v>
       </c>
       <c r="E16" t="n">
-        <v>48.64</v>
+        <v>15.77</v>
       </c>
       <c r="F16" t="n">
-        <v>45.38</v>
+        <v>15.65</v>
       </c>
       <c r="G16" t="n">
-        <v>47.59</v>
+        <v>17.29</v>
       </c>
       <c r="H16" t="n">
-        <v>2.131</v>
+        <v>-0.162</v>
       </c>
       <c r="I16" t="n">
-        <v>1.931</v>
+        <v>0.039</v>
       </c>
       <c r="J16" t="n">
-        <v>82.48</v>
+        <v>60.35</v>
       </c>
       <c r="K16" t="n">
-        <v>64.04000000000001</v>
+        <v>40.49</v>
       </c>
       <c r="L16" t="n">
-        <v>119.36</v>
+        <v>100.08</v>
       </c>
       <c r="M16" t="n">
-        <v>75.12</v>
+        <v>50.27</v>
       </c>
       <c r="N16" t="n">
-        <v>65.09999999999999</v>
+        <v>48.31</v>
       </c>
       <c r="O16" t="n">
-        <v>62.26</v>
+        <v>50.17</v>
       </c>
       <c r="P16" t="n">
-        <v>3952.08</v>
+        <v>781.26</v>
       </c>
       <c r="Q16" t="n">
-        <v>3421.06</v>
+        <v>1469.33</v>
       </c>
       <c r="R16" t="n">
-        <v>1.16</v>
+        <v>0.53</v>
       </c>
       <c r="S16" t="n">
-        <v>50.8</v>
+        <v>15.88</v>
       </c>
       <c r="T16" t="n">
-        <v>52.33</v>
+        <v>16.08</v>
       </c>
       <c r="U16" t="n">
-        <v>49.71</v>
+        <v>15.76</v>
       </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
@@ -1630,69 +1630,69 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>300302</v>
+        <v>603881</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>同有科技</t>
+          <t>数据港</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.45</v>
+        <v>41.19</v>
       </c>
       <c r="D17" t="n">
-        <v>3.08</v>
+        <v>2.49</v>
       </c>
       <c r="E17" t="n">
-        <v>22.35</v>
+        <v>39.89</v>
       </c>
       <c r="F17" t="n">
-        <v>20.96</v>
+        <v>38.54</v>
       </c>
       <c r="G17" t="n">
-        <v>21.85</v>
+        <v>37.94</v>
       </c>
       <c r="H17" t="n">
-        <v>0.447</v>
+        <v>0.617</v>
       </c>
       <c r="I17" t="n">
-        <v>0.257</v>
+        <v>0.224</v>
       </c>
       <c r="J17" t="n">
-        <v>79.97</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>60.39</v>
+        <v>71.34</v>
       </c>
       <c r="L17" t="n">
-        <v>119.12</v>
+        <v>105.27</v>
       </c>
       <c r="M17" t="n">
-        <v>74.22</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>62.82</v>
+        <v>61.8</v>
       </c>
       <c r="O17" t="n">
-        <v>58.38</v>
+        <v>57.13</v>
       </c>
       <c r="P17" t="n">
-        <v>3343.64</v>
+        <v>8134.69</v>
       </c>
       <c r="Q17" t="n">
-        <v>4731.27</v>
+        <v>6633.35</v>
       </c>
       <c r="R17" t="n">
-        <v>0.71</v>
+        <v>1.23</v>
       </c>
       <c r="S17" t="n">
-        <v>23.2</v>
+        <v>40.94</v>
       </c>
       <c r="T17" t="n">
-        <v>23.58</v>
+        <v>41.62</v>
       </c>
       <c r="U17" t="n">
-        <v>23</v>
+        <v>40.3</v>
       </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
@@ -1703,69 +1703,69 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20</v>
+        <v>300017</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>深华发A</t>
+          <t>网宿科技</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.03</v>
+        <v>18.67</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2</v>
+        <v>2.81</v>
       </c>
       <c r="E18" t="n">
-        <v>15.77</v>
+        <v>18.19</v>
       </c>
       <c r="F18" t="n">
-        <v>15.65</v>
+        <v>17.48</v>
       </c>
       <c r="G18" t="n">
-        <v>17.29</v>
+        <v>17.52</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.162</v>
+        <v>0.062</v>
       </c>
       <c r="I18" t="n">
-        <v>0.039</v>
+        <v>-0.054</v>
       </c>
       <c r="J18" t="n">
-        <v>60.35</v>
+        <v>70.98</v>
       </c>
       <c r="K18" t="n">
-        <v>40.49</v>
+        <v>59.13</v>
       </c>
       <c r="L18" t="n">
-        <v>100.08</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>50.27</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>48.31</v>
+        <v>56.47</v>
       </c>
       <c r="O18" t="n">
-        <v>50.17</v>
+        <v>55.14</v>
       </c>
       <c r="P18" t="n">
-        <v>781.26</v>
+        <v>29908.57</v>
       </c>
       <c r="Q18" t="n">
-        <v>1469.33</v>
+        <v>21403.83</v>
       </c>
       <c r="R18" t="n">
-        <v>0.53</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>15.88</v>
+        <v>19.1</v>
       </c>
       <c r="T18" t="n">
-        <v>16.08</v>
+        <v>19.48</v>
       </c>
       <c r="U18" t="n">
-        <v>15.76</v>
+        <v>18.42</v>
       </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
@@ -1776,69 +1776,69 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>603881</v>
+        <v>300418</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>数据港</t>
+          <t>昆仑万维</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>41.19</v>
+        <v>50.85</v>
       </c>
       <c r="D19" t="n">
-        <v>2.49</v>
+        <v>2.21</v>
       </c>
       <c r="E19" t="n">
-        <v>39.89</v>
+        <v>50.7</v>
       </c>
       <c r="F19" t="n">
-        <v>38.54</v>
+        <v>49.51</v>
       </c>
       <c r="G19" t="n">
-        <v>37.94</v>
+        <v>50.17</v>
       </c>
       <c r="H19" t="n">
-        <v>0.617</v>
+        <v>-0.893</v>
       </c>
       <c r="I19" t="n">
-        <v>0.224</v>
+        <v>-1.165</v>
       </c>
       <c r="J19" t="n">
-        <v>82.65000000000001</v>
+        <v>62.57</v>
       </c>
       <c r="K19" t="n">
-        <v>71.34</v>
+        <v>52.94</v>
       </c>
       <c r="L19" t="n">
-        <v>105.27</v>
+        <v>81.83</v>
       </c>
       <c r="M19" t="n">
-        <v>72.51000000000001</v>
+        <v>55.13</v>
       </c>
       <c r="N19" t="n">
-        <v>61.8</v>
+        <v>50.11</v>
       </c>
       <c r="O19" t="n">
-        <v>57.13</v>
+        <v>49.41</v>
       </c>
       <c r="P19" t="n">
-        <v>8134.69</v>
+        <v>4851.13</v>
       </c>
       <c r="Q19" t="n">
-        <v>6633.35</v>
+        <v>6155.48</v>
       </c>
       <c r="R19" t="n">
-        <v>1.23</v>
+        <v>0.79</v>
       </c>
       <c r="S19" t="n">
-        <v>40.94</v>
+        <v>50.58</v>
       </c>
       <c r="T19" t="n">
-        <v>41.62</v>
+        <v>51.15</v>
       </c>
       <c r="U19" t="n">
-        <v>40.3</v>
+        <v>50.1</v>
       </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
@@ -1849,69 +1849,69 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>300017</v>
+        <v>2230</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>网宿科技</t>
+          <t>科大讯飞</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>18.67</v>
+        <v>48.33</v>
       </c>
       <c r="D20" t="n">
-        <v>2.81</v>
+        <v>1.15</v>
       </c>
       <c r="E20" t="n">
-        <v>18.19</v>
+        <v>47.77</v>
       </c>
       <c r="F20" t="n">
-        <v>17.48</v>
+        <v>46.93</v>
       </c>
       <c r="G20" t="n">
-        <v>17.52</v>
+        <v>47.6</v>
       </c>
       <c r="H20" t="n">
-        <v>0.062</v>
+        <v>-1.327</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.054</v>
+        <v>-1.772</v>
       </c>
       <c r="J20" t="n">
-        <v>70.98</v>
+        <v>75.19</v>
       </c>
       <c r="K20" t="n">
-        <v>59.13</v>
+        <v>59.21</v>
       </c>
       <c r="L20" t="n">
-        <v>94.68000000000001</v>
+        <v>107.15</v>
       </c>
       <c r="M20" t="n">
-        <v>64.45999999999999</v>
+        <v>63.2</v>
       </c>
       <c r="N20" t="n">
-        <v>56.47</v>
+        <v>48.68</v>
       </c>
       <c r="O20" t="n">
-        <v>55.14</v>
+        <v>44.01</v>
       </c>
       <c r="P20" t="n">
-        <v>29908.57</v>
+        <v>3662.68</v>
       </c>
       <c r="Q20" t="n">
-        <v>21403.83</v>
+        <v>3110.97</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>19.1</v>
+        <v>48.5</v>
       </c>
       <c r="T20" t="n">
-        <v>19.48</v>
+        <v>48.64</v>
       </c>
       <c r="U20" t="n">
-        <v>18.42</v>
+        <v>47.87</v>
       </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
@@ -1922,69 +1922,69 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>300418</v>
+        <v>300058</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>昆仑万维</t>
+          <t>蓝色光标</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>50.85</v>
+        <v>17.27</v>
       </c>
       <c r="D21" t="n">
-        <v>2.21</v>
+        <v>4.41</v>
       </c>
       <c r="E21" t="n">
-        <v>50.7</v>
+        <v>16.65</v>
       </c>
       <c r="F21" t="n">
-        <v>49.51</v>
+        <v>15.35</v>
       </c>
       <c r="G21" t="n">
-        <v>50.17</v>
+        <v>14.91</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.893</v>
+        <v>0.019</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.165</v>
+        <v>-0.435</v>
       </c>
       <c r="J21" t="n">
-        <v>62.57</v>
+        <v>81.87</v>
       </c>
       <c r="K21" t="n">
-        <v>52.94</v>
+        <v>67.98</v>
       </c>
       <c r="L21" t="n">
-        <v>81.83</v>
+        <v>109.64</v>
       </c>
       <c r="M21" t="n">
-        <v>55.13</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>50.11</v>
+        <v>63.83</v>
       </c>
       <c r="O21" t="n">
-        <v>49.41</v>
+        <v>55.73</v>
       </c>
       <c r="P21" t="n">
-        <v>4851.13</v>
+        <v>65844.52</v>
       </c>
       <c r="Q21" t="n">
-        <v>6155.48</v>
+        <v>33390.98</v>
       </c>
       <c r="R21" t="n">
-        <v>0.79</v>
+        <v>1.97</v>
       </c>
       <c r="S21" t="n">
-        <v>50.58</v>
+        <v>16.93</v>
       </c>
       <c r="T21" t="n">
-        <v>51.15</v>
+        <v>17.48</v>
       </c>
       <c r="U21" t="n">
-        <v>50.1</v>
+        <v>16.8</v>
       </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
@@ -1995,69 +1995,69 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2230</v>
+        <v>300496</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>科大讯飞</t>
+          <t>中科创达</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>48.33</v>
+        <v>61.53</v>
       </c>
       <c r="D22" t="n">
-        <v>1.15</v>
+        <v>1.84</v>
       </c>
       <c r="E22" t="n">
-        <v>47.77</v>
+        <v>60.66</v>
       </c>
       <c r="F22" t="n">
-        <v>46.93</v>
+        <v>59.24</v>
       </c>
       <c r="G22" t="n">
-        <v>47.6</v>
+        <v>60.6</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.327</v>
+        <v>-2.04</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.772</v>
+        <v>-2.655</v>
       </c>
       <c r="J22" t="n">
-        <v>75.19</v>
+        <v>75.17</v>
       </c>
       <c r="K22" t="n">
-        <v>59.21</v>
+        <v>57.16</v>
       </c>
       <c r="L22" t="n">
-        <v>107.15</v>
+        <v>111.17</v>
       </c>
       <c r="M22" t="n">
-        <v>63.2</v>
+        <v>61.63</v>
       </c>
       <c r="N22" t="n">
-        <v>48.68</v>
+        <v>48.87</v>
       </c>
       <c r="O22" t="n">
-        <v>44.01</v>
+        <v>44.34</v>
       </c>
       <c r="P22" t="n">
-        <v>3662.68</v>
+        <v>1046.85</v>
       </c>
       <c r="Q22" t="n">
-        <v>3110.97</v>
+        <v>996.37</v>
       </c>
       <c r="R22" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="S22" t="n">
-        <v>48.5</v>
+        <v>61.3</v>
       </c>
       <c r="T22" t="n">
-        <v>48.64</v>
+        <v>61.89</v>
       </c>
       <c r="U22" t="n">
-        <v>47.87</v>
+        <v>60.84</v>
       </c>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
@@ -2068,69 +2068,69 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>300058</v>
+        <v>547</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>蓝色光标</t>
+          <t>航天发展</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>17.27</v>
+        <v>27.17</v>
       </c>
       <c r="D23" t="n">
-        <v>4.41</v>
+        <v>2.84</v>
       </c>
       <c r="E23" t="n">
-        <v>16.65</v>
+        <v>26.89</v>
       </c>
       <c r="F23" t="n">
-        <v>15.35</v>
+        <v>26.95</v>
       </c>
       <c r="G23" t="n">
-        <v>14.91</v>
+        <v>27.71</v>
       </c>
       <c r="H23" t="n">
-        <v>0.019</v>
+        <v>-0.863</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.435</v>
+        <v>-0.822</v>
       </c>
       <c r="J23" t="n">
-        <v>81.87</v>
+        <v>33.87</v>
       </c>
       <c r="K23" t="n">
-        <v>67.98</v>
+        <v>31.58</v>
       </c>
       <c r="L23" t="n">
-        <v>109.64</v>
+        <v>38.45</v>
       </c>
       <c r="M23" t="n">
-        <v>77.84999999999999</v>
+        <v>50.67</v>
       </c>
       <c r="N23" t="n">
-        <v>63.83</v>
+        <v>45.97</v>
       </c>
       <c r="O23" t="n">
-        <v>55.73</v>
+        <v>47.15</v>
       </c>
       <c r="P23" t="n">
-        <v>65844.52</v>
+        <v>19607.93</v>
       </c>
       <c r="Q23" t="n">
-        <v>33390.98</v>
+        <v>17654.22</v>
       </c>
       <c r="R23" t="n">
-        <v>1.97</v>
+        <v>1.11</v>
       </c>
       <c r="S23" t="n">
-        <v>16.93</v>
+        <v>26.6</v>
       </c>
       <c r="T23" t="n">
-        <v>17.48</v>
+        <v>27.34</v>
       </c>
       <c r="U23" t="n">
-        <v>16.8</v>
+        <v>26.12</v>
       </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
@@ -2141,69 +2141,69 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>300496</v>
+        <v>2202</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>中科创达</t>
+          <t>金风科技</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>61.53</v>
+        <v>25.3</v>
       </c>
       <c r="D24" t="n">
-        <v>1.84</v>
+        <v>4.81</v>
       </c>
       <c r="E24" t="n">
-        <v>60.66</v>
+        <v>24.24</v>
       </c>
       <c r="F24" t="n">
-        <v>59.24</v>
+        <v>24.4</v>
       </c>
       <c r="G24" t="n">
-        <v>60.6</v>
+        <v>26.46</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.04</v>
+        <v>-1.039</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.655</v>
+        <v>-0.801</v>
       </c>
       <c r="J24" t="n">
-        <v>75.17</v>
+        <v>35.18</v>
       </c>
       <c r="K24" t="n">
-        <v>57.16</v>
+        <v>22.39</v>
       </c>
       <c r="L24" t="n">
-        <v>111.17</v>
+        <v>60.75</v>
       </c>
       <c r="M24" t="n">
-        <v>61.63</v>
+        <v>54.65</v>
       </c>
       <c r="N24" t="n">
-        <v>48.87</v>
+        <v>45.78</v>
       </c>
       <c r="O24" t="n">
-        <v>44.34</v>
+        <v>47.59</v>
       </c>
       <c r="P24" t="n">
-        <v>1046.85</v>
+        <v>27970.37</v>
       </c>
       <c r="Q24" t="n">
-        <v>996.37</v>
+        <v>24078.93</v>
       </c>
       <c r="R24" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="S24" t="n">
-        <v>61.3</v>
+        <v>24.35</v>
       </c>
       <c r="T24" t="n">
-        <v>61.89</v>
+        <v>25.34</v>
       </c>
       <c r="U24" t="n">
-        <v>60.84</v>
+        <v>24.1</v>
       </c>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
@@ -2214,69 +2214,69 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>547</v>
+        <v>301128</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>航天发展</t>
+          <t>强瑞技术</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>27.17</v>
+        <v>173.14</v>
       </c>
       <c r="D25" t="n">
-        <v>2.84</v>
+        <v>5.78</v>
       </c>
       <c r="E25" t="n">
-        <v>26.89</v>
+        <v>165.23</v>
       </c>
       <c r="F25" t="n">
-        <v>26.95</v>
+        <v>158.02</v>
       </c>
       <c r="G25" t="n">
-        <v>27.71</v>
+        <v>145.01</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.863</v>
+        <v>13.828</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.822</v>
+        <v>11.884</v>
       </c>
       <c r="J25" t="n">
-        <v>33.87</v>
+        <v>79.81</v>
       </c>
       <c r="K25" t="n">
-        <v>31.58</v>
+        <v>79</v>
       </c>
       <c r="L25" t="n">
-        <v>38.45</v>
+        <v>81.41</v>
       </c>
       <c r="M25" t="n">
-        <v>50.67</v>
+        <v>77.27</v>
       </c>
       <c r="N25" t="n">
-        <v>45.97</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>47.15</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>19607.93</v>
+        <v>709.83</v>
       </c>
       <c r="Q25" t="n">
-        <v>17654.22</v>
+        <v>955.46</v>
       </c>
       <c r="R25" t="n">
-        <v>1.11</v>
+        <v>0.74</v>
       </c>
       <c r="S25" t="n">
-        <v>26.6</v>
+        <v>161</v>
       </c>
       <c r="T25" t="n">
-        <v>27.34</v>
+        <v>173.22</v>
       </c>
       <c r="U25" t="n">
-        <v>26.12</v>
+        <v>161</v>
       </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
@@ -2287,69 +2287,69 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2202</v>
+        <v>601899</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>金风科技</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25.3</v>
+        <v>34.8</v>
       </c>
       <c r="D26" t="n">
-        <v>4.81</v>
+        <v>3.39</v>
       </c>
       <c r="E26" t="n">
-        <v>24.24</v>
+        <v>34.15</v>
       </c>
       <c r="F26" t="n">
-        <v>24.4</v>
+        <v>33.6</v>
       </c>
       <c r="G26" t="n">
-        <v>26.46</v>
+        <v>33.16</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.039</v>
+        <v>-0.537</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.801</v>
+        <v>-0.893</v>
       </c>
       <c r="J26" t="n">
-        <v>35.18</v>
+        <v>73.58</v>
       </c>
       <c r="K26" t="n">
-        <v>22.39</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>60.75</v>
+        <v>86.66</v>
       </c>
       <c r="M26" t="n">
-        <v>54.65</v>
+        <v>64.23</v>
       </c>
       <c r="N26" t="n">
-        <v>45.78</v>
+        <v>53.89</v>
       </c>
       <c r="O26" t="n">
-        <v>47.59</v>
+        <v>49.71</v>
       </c>
       <c r="P26" t="n">
-        <v>27970.37</v>
+        <v>29884.57</v>
       </c>
       <c r="Q26" t="n">
-        <v>24078.93</v>
+        <v>29693.57</v>
       </c>
       <c r="R26" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="S26" t="n">
-        <v>24.35</v>
+        <v>34.49</v>
       </c>
       <c r="T26" t="n">
-        <v>25.34</v>
+        <v>34.95</v>
       </c>
       <c r="U26" t="n">
-        <v>24.1</v>
+        <v>34.35</v>
       </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
@@ -2360,69 +2360,69 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>301128</v>
+        <v>600219</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>强瑞技术</t>
+          <t>南山铝业</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>173.14</v>
+        <v>6.38</v>
       </c>
       <c r="D27" t="n">
-        <v>5.78</v>
+        <v>3.57</v>
       </c>
       <c r="E27" t="n">
-        <v>165.23</v>
+        <v>6.28</v>
       </c>
       <c r="F27" t="n">
-        <v>158.02</v>
+        <v>6.19</v>
       </c>
       <c r="G27" t="n">
-        <v>145.01</v>
+        <v>6.17</v>
       </c>
       <c r="H27" t="n">
-        <v>13.828</v>
+        <v>-0.135</v>
       </c>
       <c r="I27" t="n">
-        <v>11.884</v>
+        <v>-0.175</v>
       </c>
       <c r="J27" t="n">
-        <v>79.81</v>
+        <v>68.06</v>
       </c>
       <c r="K27" t="n">
-        <v>79</v>
+        <v>56.9</v>
       </c>
       <c r="L27" t="n">
-        <v>81.41</v>
+        <v>90.36</v>
       </c>
       <c r="M27" t="n">
-        <v>77.27</v>
+        <v>59.04</v>
       </c>
       <c r="N27" t="n">
-        <v>73.70999999999999</v>
+        <v>50.55</v>
       </c>
       <c r="O27" t="n">
-        <v>70.01000000000001</v>
+        <v>49.65</v>
       </c>
       <c r="P27" t="n">
-        <v>709.83</v>
+        <v>33384.37</v>
       </c>
       <c r="Q27" t="n">
-        <v>955.46</v>
+        <v>25665.78</v>
       </c>
       <c r="R27" t="n">
-        <v>0.74</v>
+        <v>1.3</v>
       </c>
       <c r="S27" t="n">
-        <v>161</v>
+        <v>6.28</v>
       </c>
       <c r="T27" t="n">
-        <v>173.22</v>
+        <v>6.39</v>
       </c>
       <c r="U27" t="n">
-        <v>161</v>
+        <v>6.23</v>
       </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
@@ -2433,69 +2433,69 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>601899</v>
+        <v>601939</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>建设银行</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>34.8</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>3.39</v>
+        <v>0.43</v>
       </c>
       <c r="E28" t="n">
-        <v>34.15</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>33.6</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>33.16</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.537</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.893</v>
+        <v>0.1</v>
       </c>
       <c r="J28" t="n">
-        <v>73.58</v>
+        <v>37.9</v>
       </c>
       <c r="K28" t="n">
-        <v>67.04000000000001</v>
+        <v>40.94</v>
       </c>
       <c r="L28" t="n">
-        <v>86.66</v>
+        <v>31.8</v>
       </c>
       <c r="M28" t="n">
-        <v>64.23</v>
+        <v>52.75</v>
       </c>
       <c r="N28" t="n">
-        <v>53.89</v>
+        <v>53.86</v>
       </c>
       <c r="O28" t="n">
-        <v>49.71</v>
+        <v>55.02</v>
       </c>
       <c r="P28" t="n">
-        <v>29884.57</v>
+        <v>5311.53</v>
       </c>
       <c r="Q28" t="n">
-        <v>29693.57</v>
+        <v>9180.809999999999</v>
       </c>
       <c r="R28" t="n">
-        <v>1.01</v>
+        <v>0.58</v>
       </c>
       <c r="S28" t="n">
-        <v>34.49</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="T28" t="n">
-        <v>34.95</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="U28" t="n">
-        <v>34.35</v>
+        <v>9.27</v>
       </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
@@ -2506,69 +2506,69 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>600219</v>
+        <v>600048</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>南山铝业</t>
+          <t>保利发展</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6.38</v>
+        <v>5.95</v>
       </c>
       <c r="D29" t="n">
-        <v>3.57</v>
+        <v>3.84</v>
       </c>
       <c r="E29" t="n">
-        <v>6.28</v>
+        <v>5.71</v>
       </c>
       <c r="F29" t="n">
-        <v>6.19</v>
+        <v>5.7</v>
       </c>
       <c r="G29" t="n">
-        <v>6.17</v>
+        <v>5.89</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.135</v>
+        <v>-0.196</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.175</v>
+        <v>-0.221</v>
       </c>
       <c r="J29" t="n">
-        <v>68.06</v>
+        <v>55.17</v>
       </c>
       <c r="K29" t="n">
-        <v>56.9</v>
+        <v>33.54</v>
       </c>
       <c r="L29" t="n">
-        <v>90.36</v>
+        <v>98.43000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>59.04</v>
+        <v>64.84</v>
       </c>
       <c r="N29" t="n">
         <v>50.55</v>
       </c>
       <c r="O29" t="n">
-        <v>49.65</v>
+        <v>45.4</v>
       </c>
       <c r="P29" t="n">
-        <v>33384.37</v>
+        <v>17815.86</v>
       </c>
       <c r="Q29" t="n">
-        <v>25665.78</v>
+        <v>10832.24</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="S29" t="n">
-        <v>6.28</v>
+        <v>5.78</v>
       </c>
       <c r="T29" t="n">
-        <v>6.39</v>
+        <v>5.96</v>
       </c>
       <c r="U29" t="n">
-        <v>6.23</v>
+        <v>5.74</v>
       </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
@@ -2579,69 +2579,69 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>601939</v>
+        <v>600941</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>建设银行</t>
+          <t>中国移动</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9.359999999999999</v>
+        <v>93.55</v>
       </c>
       <c r="D30" t="n">
-        <v>0.43</v>
+        <v>-0.12</v>
       </c>
       <c r="E30" t="n">
-        <v>9.300000000000001</v>
+        <v>93.77</v>
       </c>
       <c r="F30" t="n">
-        <v>9.380000000000001</v>
+        <v>93.62</v>
       </c>
       <c r="G30" t="n">
-        <v>9.359999999999999</v>
+        <v>94.41</v>
       </c>
       <c r="H30" t="n">
-        <v>0.06900000000000001</v>
+        <v>-0.551</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>37.9</v>
+        <v>56.77</v>
       </c>
       <c r="K30" t="n">
-        <v>40.94</v>
+        <v>53.16</v>
       </c>
       <c r="L30" t="n">
-        <v>31.8</v>
+        <v>63.99</v>
       </c>
       <c r="M30" t="n">
-        <v>52.75</v>
+        <v>42.86</v>
       </c>
       <c r="N30" t="n">
-        <v>53.86</v>
+        <v>42.99</v>
       </c>
       <c r="O30" t="n">
-        <v>55.02</v>
+        <v>43.56</v>
       </c>
       <c r="P30" t="n">
-        <v>5311.53</v>
+        <v>636.04</v>
       </c>
       <c r="Q30" t="n">
-        <v>9180.809999999999</v>
+        <v>850.51</v>
       </c>
       <c r="R30" t="n">
-        <v>0.58</v>
+        <v>0.75</v>
       </c>
       <c r="S30" t="n">
-        <v>9.289999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="T30" t="n">
-        <v>9.380000000000001</v>
+        <v>93.97</v>
       </c>
       <c r="U30" t="n">
-        <v>9.27</v>
+        <v>93.31</v>
       </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
@@ -2652,69 +2652,69 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>600048</v>
+        <v>2352</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>保利发展</t>
+          <t>顺丰控股</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5.95</v>
+        <v>37.18</v>
       </c>
       <c r="D31" t="n">
-        <v>3.84</v>
+        <v>0.57</v>
       </c>
       <c r="E31" t="n">
-        <v>5.71</v>
+        <v>37.4</v>
       </c>
       <c r="F31" t="n">
-        <v>5.7</v>
+        <v>37.67</v>
       </c>
       <c r="G31" t="n">
-        <v>5.89</v>
+        <v>37.13</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.196</v>
+        <v>0.004</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.221</v>
+        <v>-0.017</v>
       </c>
       <c r="J31" t="n">
-        <v>55.17</v>
+        <v>36.55</v>
       </c>
       <c r="K31" t="n">
-        <v>33.54</v>
+        <v>49.84</v>
       </c>
       <c r="L31" t="n">
-        <v>98.43000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="M31" t="n">
-        <v>64.84</v>
+        <v>44.27</v>
       </c>
       <c r="N31" t="n">
-        <v>50.55</v>
+        <v>47.96</v>
       </c>
       <c r="O31" t="n">
-        <v>45.4</v>
+        <v>48.17</v>
       </c>
       <c r="P31" t="n">
-        <v>17815.86</v>
+        <v>1735.69</v>
       </c>
       <c r="Q31" t="n">
-        <v>10832.24</v>
+        <v>2182.95</v>
       </c>
       <c r="R31" t="n">
-        <v>1.64</v>
+        <v>0.8</v>
       </c>
       <c r="S31" t="n">
-        <v>5.78</v>
+        <v>37.12</v>
       </c>
       <c r="T31" t="n">
-        <v>5.96</v>
+        <v>37.27</v>
       </c>
       <c r="U31" t="n">
-        <v>5.74</v>
+        <v>36.81</v>
       </c>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
@@ -2725,69 +2725,69 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>600941</v>
+        <v>603803</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>中国移动</t>
+          <t>瑞斯康达</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>93.55</v>
+        <v>15</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.12</v>
+        <v>-1.7</v>
       </c>
       <c r="E32" t="n">
-        <v>93.77</v>
+        <v>14.49</v>
       </c>
       <c r="F32" t="n">
-        <v>93.62</v>
+        <v>13.82</v>
       </c>
       <c r="G32" t="n">
-        <v>94.41</v>
+        <v>13.89</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.551</v>
+        <v>0.702</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5590000000000001</v>
+        <v>0.674</v>
       </c>
       <c r="J32" t="n">
-        <v>56.77</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>53.16</v>
+        <v>58.86</v>
       </c>
       <c r="L32" t="n">
-        <v>63.99</v>
+        <v>79.55</v>
       </c>
       <c r="M32" t="n">
-        <v>42.86</v>
+        <v>64.41</v>
       </c>
       <c r="N32" t="n">
-        <v>42.99</v>
+        <v>61.18</v>
       </c>
       <c r="O32" t="n">
-        <v>43.56</v>
+        <v>59.84</v>
       </c>
       <c r="P32" t="n">
-        <v>636.04</v>
+        <v>11987.76</v>
       </c>
       <c r="Q32" t="n">
-        <v>850.51</v>
+        <v>9170.870000000001</v>
       </c>
       <c r="R32" t="n">
-        <v>0.75</v>
+        <v>1.31</v>
       </c>
       <c r="S32" t="n">
-        <v>93.59999999999999</v>
+        <v>16.79</v>
       </c>
       <c r="T32" t="n">
-        <v>93.97</v>
+        <v>16.79</v>
       </c>
       <c r="U32" t="n">
-        <v>93.31</v>
+        <v>14.83</v>
       </c>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
@@ -2798,69 +2798,69 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2352</v>
+        <v>2624</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>顺丰控股</t>
+          <t>完美世界</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>37.18</v>
+        <v>19.4</v>
       </c>
       <c r="D33" t="n">
-        <v>0.57</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>37.4</v>
+        <v>19.85</v>
       </c>
       <c r="F33" t="n">
-        <v>37.67</v>
+        <v>19.45</v>
       </c>
       <c r="G33" t="n">
-        <v>37.13</v>
+        <v>18.79</v>
       </c>
       <c r="H33" t="n">
-        <v>0.004</v>
+        <v>0.114</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.017</v>
+        <v>-0.036</v>
       </c>
       <c r="J33" t="n">
-        <v>36.55</v>
+        <v>68.31</v>
       </c>
       <c r="K33" t="n">
-        <v>49.84</v>
+        <v>71.97</v>
       </c>
       <c r="L33" t="n">
-        <v>9.99</v>
+        <v>60.98</v>
       </c>
       <c r="M33" t="n">
-        <v>44.27</v>
+        <v>49.93</v>
       </c>
       <c r="N33" t="n">
-        <v>47.96</v>
+        <v>51.37</v>
       </c>
       <c r="O33" t="n">
-        <v>48.17</v>
+        <v>51.83</v>
       </c>
       <c r="P33" t="n">
-        <v>1735.69</v>
+        <v>6403.84</v>
       </c>
       <c r="Q33" t="n">
-        <v>2182.95</v>
+        <v>5635.93</v>
       </c>
       <c r="R33" t="n">
-        <v>0.8</v>
+        <v>1.14</v>
       </c>
       <c r="S33" t="n">
-        <v>37.12</v>
+        <v>19.51</v>
       </c>
       <c r="T33" t="n">
-        <v>37.27</v>
+        <v>19.85</v>
       </c>
       <c r="U33" t="n">
-        <v>36.81</v>
+        <v>19.07</v>
       </c>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
@@ -2871,69 +2871,69 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>603803</v>
+        <v>2558</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>瑞斯康达</t>
+          <t>巨人网络</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>15</v>
+        <v>31.75</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.7</v>
+        <v>0.73</v>
       </c>
       <c r="E34" t="n">
-        <v>14.49</v>
+        <v>33.08</v>
       </c>
       <c r="F34" t="n">
-        <v>13.82</v>
+        <v>33.18</v>
       </c>
       <c r="G34" t="n">
-        <v>13.89</v>
+        <v>32.84</v>
       </c>
       <c r="H34" t="n">
-        <v>0.702</v>
+        <v>-1.09</v>
       </c>
       <c r="I34" t="n">
-        <v>0.674</v>
+        <v>-1.336</v>
       </c>
       <c r="J34" t="n">
-        <v>65.76000000000001</v>
+        <v>36.41</v>
       </c>
       <c r="K34" t="n">
-        <v>58.86</v>
+        <v>48.32</v>
       </c>
       <c r="L34" t="n">
-        <v>79.55</v>
+        <v>12.59</v>
       </c>
       <c r="M34" t="n">
-        <v>64.41</v>
+        <v>40.76</v>
       </c>
       <c r="N34" t="n">
-        <v>61.18</v>
+        <v>41.68</v>
       </c>
       <c r="O34" t="n">
-        <v>59.84</v>
+        <v>40.46</v>
       </c>
       <c r="P34" t="n">
-        <v>11987.76</v>
+        <v>6986.68</v>
       </c>
       <c r="Q34" t="n">
-        <v>9170.870000000001</v>
+        <v>4934.71</v>
       </c>
       <c r="R34" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="S34" t="n">
-        <v>16.79</v>
+        <v>31.94</v>
       </c>
       <c r="T34" t="n">
-        <v>16.79</v>
+        <v>32.05</v>
       </c>
       <c r="U34" t="n">
-        <v>14.83</v>
+        <v>31.1</v>
       </c>
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
@@ -2944,69 +2944,69 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2624</v>
+        <v>601088</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>完美世界</t>
+          <t>中国神华</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>19.4</v>
+        <v>45.66</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.42</v>
       </c>
       <c r="E35" t="n">
-        <v>19.85</v>
+        <v>46.38</v>
       </c>
       <c r="F35" t="n">
-        <v>19.45</v>
+        <v>46.9</v>
       </c>
       <c r="G35" t="n">
-        <v>18.79</v>
+        <v>47.57</v>
       </c>
       <c r="H35" t="n">
-        <v>0.114</v>
+        <v>0.161</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.036</v>
+        <v>0.575</v>
       </c>
       <c r="J35" t="n">
-        <v>68.31</v>
+        <v>21.71</v>
       </c>
       <c r="K35" t="n">
-        <v>71.97</v>
+        <v>31.51</v>
       </c>
       <c r="L35" t="n">
-        <v>60.98</v>
+        <v>2.12</v>
       </c>
       <c r="M35" t="n">
-        <v>49.93</v>
+        <v>28.49</v>
       </c>
       <c r="N35" t="n">
-        <v>51.37</v>
+        <v>41.51</v>
       </c>
       <c r="O35" t="n">
-        <v>51.83</v>
+        <v>49.82</v>
       </c>
       <c r="P35" t="n">
-        <v>6403.84</v>
+        <v>3015.77</v>
       </c>
       <c r="Q35" t="n">
-        <v>5635.93</v>
+        <v>3691.07</v>
       </c>
       <c r="R35" t="n">
-        <v>1.14</v>
+        <v>0.82</v>
       </c>
       <c r="S35" t="n">
-        <v>19.51</v>
+        <v>46.11</v>
       </c>
       <c r="T35" t="n">
-        <v>19.85</v>
+        <v>46.22</v>
       </c>
       <c r="U35" t="n">
-        <v>19.07</v>
+        <v>45.42</v>
       </c>
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
@@ -3017,69 +3017,69 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2558</v>
+        <v>600963</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>巨人网络</t>
+          <t>岳阳林纸</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>31.75</v>
+        <v>4.76</v>
       </c>
       <c r="D36" t="n">
-        <v>0.73</v>
+        <v>-1.86</v>
       </c>
       <c r="E36" t="n">
-        <v>33.08</v>
+        <v>4.83</v>
       </c>
       <c r="F36" t="n">
-        <v>33.18</v>
+        <v>4.78</v>
       </c>
       <c r="G36" t="n">
-        <v>32.84</v>
+        <v>4.84</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.09</v>
+        <v>-0.177</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.336</v>
+        <v>-0.203</v>
       </c>
       <c r="J36" t="n">
-        <v>36.41</v>
+        <v>56.36</v>
       </c>
       <c r="K36" t="n">
-        <v>48.32</v>
+        <v>55.1</v>
       </c>
       <c r="L36" t="n">
-        <v>12.59</v>
+        <v>58.86</v>
       </c>
       <c r="M36" t="n">
-        <v>40.76</v>
+        <v>42.09</v>
       </c>
       <c r="N36" t="n">
-        <v>41.68</v>
+        <v>40.54</v>
       </c>
       <c r="O36" t="n">
-        <v>40.46</v>
+        <v>43.55</v>
       </c>
       <c r="P36" t="n">
-        <v>6986.68</v>
+        <v>2387.58</v>
       </c>
       <c r="Q36" t="n">
-        <v>4934.71</v>
+        <v>2959.72</v>
       </c>
       <c r="R36" t="n">
-        <v>1.42</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="S36" t="n">
-        <v>31.94</v>
+        <v>4.88</v>
       </c>
       <c r="T36" t="n">
-        <v>32.05</v>
+        <v>4.89</v>
       </c>
       <c r="U36" t="n">
-        <v>31.1</v>
+        <v>4.72</v>
       </c>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
@@ -3090,69 +3090,69 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>601088</v>
+        <v>601877</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>中国神华</t>
+          <t>正泰电器</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>45.66</v>
+        <v>33.52</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.42</v>
+        <v>0.93</v>
       </c>
       <c r="E37" t="n">
-        <v>46.38</v>
+        <v>33.15</v>
       </c>
       <c r="F37" t="n">
-        <v>46.9</v>
+        <v>32.56</v>
       </c>
       <c r="G37" t="n">
-        <v>47.57</v>
+        <v>33.59</v>
       </c>
       <c r="H37" t="n">
-        <v>0.161</v>
+        <v>-0.344</v>
       </c>
       <c r="I37" t="n">
-        <v>0.575</v>
+        <v>-0.261</v>
       </c>
       <c r="J37" t="n">
-        <v>21.71</v>
+        <v>66.64</v>
       </c>
       <c r="K37" t="n">
-        <v>31.51</v>
+        <v>47.64</v>
       </c>
       <c r="L37" t="n">
-        <v>2.12</v>
+        <v>104.65</v>
       </c>
       <c r="M37" t="n">
-        <v>28.49</v>
+        <v>56.97</v>
       </c>
       <c r="N37" t="n">
-        <v>41.51</v>
+        <v>50.05</v>
       </c>
       <c r="O37" t="n">
-        <v>49.82</v>
+        <v>51.15</v>
       </c>
       <c r="P37" t="n">
-        <v>3015.77</v>
+        <v>2827.32</v>
       </c>
       <c r="Q37" t="n">
-        <v>3691.07</v>
+        <v>3621.76</v>
       </c>
       <c r="R37" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="S37" t="n">
-        <v>46.11</v>
+        <v>33.11</v>
       </c>
       <c r="T37" t="n">
-        <v>46.22</v>
+        <v>33.52</v>
       </c>
       <c r="U37" t="n">
-        <v>45.42</v>
+        <v>32.85</v>
       </c>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
@@ -3163,69 +3163,69 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>600963</v>
+        <v>2049</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>岳阳林纸</t>
+          <t>紫光国微</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4.76</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.86</v>
+        <v>1.1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.83</v>
+        <v>69.64</v>
       </c>
       <c r="F38" t="n">
-        <v>4.78</v>
+        <v>67.8</v>
       </c>
       <c r="G38" t="n">
-        <v>4.84</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.177</v>
+        <v>-1.443</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.203</v>
+        <v>-2.201</v>
       </c>
       <c r="J38" t="n">
-        <v>56.36</v>
+        <v>80.81</v>
       </c>
       <c r="K38" t="n">
-        <v>55.1</v>
+        <v>63.47</v>
       </c>
       <c r="L38" t="n">
-        <v>58.86</v>
+        <v>115.48</v>
       </c>
       <c r="M38" t="n">
-        <v>42.09</v>
+        <v>68.77</v>
       </c>
       <c r="N38" t="n">
-        <v>40.54</v>
+        <v>53.9</v>
       </c>
       <c r="O38" t="n">
-        <v>43.55</v>
+        <v>47.59</v>
       </c>
       <c r="P38" t="n">
-        <v>2387.58</v>
+        <v>1616.77</v>
       </c>
       <c r="Q38" t="n">
-        <v>2959.72</v>
+        <v>1271.64</v>
       </c>
       <c r="R38" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.27</v>
       </c>
       <c r="S38" t="n">
-        <v>4.88</v>
+        <v>70.55</v>
       </c>
       <c r="T38" t="n">
-        <v>4.89</v>
+        <v>71.5</v>
       </c>
       <c r="U38" t="n">
-        <v>4.72</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
@@ -3236,69 +3236,69 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>601877</v>
+        <v>601689</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>正泰电器</t>
+          <t>拓普集团</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>33.52</v>
+        <v>60.04</v>
       </c>
       <c r="D39" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="E39" t="n">
-        <v>33.15</v>
+        <v>59.57</v>
       </c>
       <c r="F39" t="n">
-        <v>32.56</v>
+        <v>58.59</v>
       </c>
       <c r="G39" t="n">
-        <v>33.59</v>
+        <v>58.6</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.344</v>
+        <v>-1.482</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.261</v>
+        <v>-2.181</v>
       </c>
       <c r="J39" t="n">
-        <v>66.64</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>47.64</v>
+        <v>58.33</v>
       </c>
       <c r="L39" t="n">
-        <v>104.65</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>56.97</v>
+        <v>58.24</v>
       </c>
       <c r="N39" t="n">
-        <v>50.05</v>
+        <v>49.55</v>
       </c>
       <c r="O39" t="n">
-        <v>51.15</v>
+        <v>43.78</v>
       </c>
       <c r="P39" t="n">
-        <v>2827.32</v>
+        <v>2758.99</v>
       </c>
       <c r="Q39" t="n">
-        <v>3621.76</v>
+        <v>2472.04</v>
       </c>
       <c r="R39" t="n">
-        <v>0.78</v>
+        <v>1.12</v>
       </c>
       <c r="S39" t="n">
-        <v>33.11</v>
+        <v>60.22</v>
       </c>
       <c r="T39" t="n">
-        <v>33.52</v>
+        <v>60.72</v>
       </c>
       <c r="U39" t="n">
-        <v>32.85</v>
+        <v>59.22</v>
       </c>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
@@ -3309,69 +3309,69 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>紫光国微</t>
+          <t>三花智控</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>71.04000000000001</v>
+        <v>45.54</v>
       </c>
       <c r="D40" t="n">
-        <v>1.1</v>
+        <v>2.45</v>
       </c>
       <c r="E40" t="n">
-        <v>69.64</v>
+        <v>44.58</v>
       </c>
       <c r="F40" t="n">
-        <v>67.8</v>
+        <v>43.55</v>
       </c>
       <c r="G40" t="n">
-        <v>68.70999999999999</v>
+        <v>43.82</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.443</v>
+        <v>-0.9379999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.201</v>
+        <v>-1.446</v>
       </c>
       <c r="J40" t="n">
-        <v>80.81</v>
+        <v>74.66</v>
       </c>
       <c r="K40" t="n">
-        <v>63.47</v>
+        <v>61.66</v>
       </c>
       <c r="L40" t="n">
-        <v>115.48</v>
+        <v>100.66</v>
       </c>
       <c r="M40" t="n">
-        <v>68.77</v>
+        <v>66.41</v>
       </c>
       <c r="N40" t="n">
-        <v>53.9</v>
+        <v>53.95</v>
       </c>
       <c r="O40" t="n">
-        <v>47.59</v>
+        <v>47.87</v>
       </c>
       <c r="P40" t="n">
-        <v>1616.77</v>
+        <v>9022.459999999999</v>
       </c>
       <c r="Q40" t="n">
-        <v>1271.64</v>
+        <v>7243.94</v>
       </c>
       <c r="R40" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S40" t="n">
-        <v>70.55</v>
+        <v>44.8</v>
       </c>
       <c r="T40" t="n">
-        <v>71.5</v>
+        <v>45.8</v>
       </c>
       <c r="U40" t="n">
-        <v>70.31999999999999</v>
+        <v>44.56</v>
       </c>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
@@ -3382,69 +3382,69 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>688271</v>
+        <v>887</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>联影医疗</t>
+          <t>中鼎股份</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>114.7</v>
+        <v>18.82</v>
       </c>
       <c r="D41" t="n">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="E41" t="n">
-        <v>113.97</v>
+        <v>18.55</v>
       </c>
       <c r="F41" t="n">
-        <v>113.27</v>
+        <v>18.2</v>
       </c>
       <c r="G41" t="n">
-        <v>113.82</v>
+        <v>18.24</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.303</v>
+        <v>-0.376</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.942</v>
+        <v>-0.577</v>
       </c>
       <c r="J41" t="n">
-        <v>71.37</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>61.55</v>
+        <v>67.37</v>
       </c>
       <c r="L41" t="n">
-        <v>91.01000000000001</v>
+        <v>103.9</v>
       </c>
       <c r="M41" t="n">
-        <v>54.93</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>47.95</v>
+        <v>52.59</v>
       </c>
       <c r="O41" t="n">
-        <v>44</v>
+        <v>45.34</v>
       </c>
       <c r="P41" t="n">
-        <v>390.87</v>
+        <v>1356.04</v>
       </c>
       <c r="Q41" t="n">
-        <v>385.39</v>
+        <v>1649.81</v>
       </c>
       <c r="R41" t="n">
-        <v>1.01</v>
+        <v>0.82</v>
       </c>
       <c r="S41" t="n">
-        <v>113.33</v>
+        <v>18.82</v>
       </c>
       <c r="T41" t="n">
-        <v>114.98</v>
+        <v>18.92</v>
       </c>
       <c r="U41" t="n">
-        <v>112.9</v>
+        <v>18.61</v>
       </c>
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
@@ -3455,69 +3455,69 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>688608</v>
+        <v>603236</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>恒玄科技</t>
+          <t>移远通信</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>170.08</v>
+        <v>77.95</v>
       </c>
       <c r="D42" t="n">
-        <v>0.79</v>
+        <v>2.42</v>
       </c>
       <c r="E42" t="n">
-        <v>168.86</v>
+        <v>76.72</v>
       </c>
       <c r="F42" t="n">
-        <v>168.41</v>
+        <v>75.09</v>
       </c>
       <c r="G42" t="n">
-        <v>167.5</v>
+        <v>75.06</v>
       </c>
       <c r="H42" t="n">
-        <v>-5.783</v>
+        <v>-1.406</v>
       </c>
       <c r="I42" t="n">
-        <v>-7.769</v>
+        <v>-2.341</v>
       </c>
       <c r="J42" t="n">
-        <v>42.29</v>
+        <v>77.33</v>
       </c>
       <c r="K42" t="n">
-        <v>41.34</v>
+        <v>66.62</v>
       </c>
       <c r="L42" t="n">
-        <v>44.19</v>
+        <v>98.77</v>
       </c>
       <c r="M42" t="n">
-        <v>54.99</v>
+        <v>65.19</v>
       </c>
       <c r="N42" t="n">
-        <v>46.93</v>
+        <v>54.19</v>
       </c>
       <c r="O42" t="n">
-        <v>42.35</v>
+        <v>46.22</v>
       </c>
       <c r="P42" t="n">
-        <v>341.27</v>
+        <v>612.88</v>
       </c>
       <c r="Q42" t="n">
-        <v>339.71</v>
+        <v>510.12</v>
       </c>
       <c r="R42" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="S42" t="n">
-        <v>170.82</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="T42" t="n">
-        <v>171.9</v>
+        <v>78.38</v>
       </c>
       <c r="U42" t="n">
-        <v>168.13</v>
+        <v>76.88</v>
       </c>
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
@@ -3528,69 +3528,69 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>688099</v>
+        <v>603072</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>晶晨股份</t>
+          <t>天和磁材</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>83.20999999999999</v>
+        <v>37.17</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2</v>
+        <v>0.54</v>
       </c>
       <c r="E43" t="n">
-        <v>82.34999999999999</v>
+        <v>36.83</v>
       </c>
       <c r="F43" t="n">
-        <v>79.88</v>
+        <v>36.3</v>
       </c>
       <c r="G43" t="n">
-        <v>82.05</v>
+        <v>36.45</v>
       </c>
       <c r="H43" t="n">
-        <v>-1.62</v>
+        <v>-0.959</v>
       </c>
       <c r="I43" t="n">
-        <v>-2.21</v>
+        <v>-1.321</v>
       </c>
       <c r="J43" t="n">
-        <v>67.40000000000001</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>52.99</v>
+        <v>67.41</v>
       </c>
       <c r="L43" t="n">
-        <v>96.23999999999999</v>
+        <v>83.98</v>
       </c>
       <c r="M43" t="n">
-        <v>60.51</v>
+        <v>62.46</v>
       </c>
       <c r="N43" t="n">
-        <v>51.09</v>
+        <v>48.28</v>
       </c>
       <c r="O43" t="n">
-        <v>48.24</v>
+        <v>44.05</v>
       </c>
       <c r="P43" t="n">
-        <v>1002.13</v>
+        <v>226.91</v>
       </c>
       <c r="Q43" t="n">
-        <v>946.96</v>
+        <v>226.37</v>
       </c>
       <c r="R43" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="S43" t="n">
-        <v>84.48999999999999</v>
+        <v>37.3</v>
       </c>
       <c r="T43" t="n">
-        <v>84.58</v>
+        <v>37.3</v>
       </c>
       <c r="U43" t="n">
-        <v>82.55</v>
+        <v>36.81</v>
       </c>
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
@@ -3601,69 +3601,69 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>688332</v>
+        <v>301023</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>中科蓝讯</t>
+          <t>奕帆传动</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>126.57</v>
+        <v>40.22</v>
       </c>
       <c r="D44" t="n">
-        <v>0.79</v>
+        <v>1.11</v>
       </c>
       <c r="E44" t="n">
-        <v>126.18</v>
+        <v>39.96</v>
       </c>
       <c r="F44" t="n">
-        <v>122.9</v>
+        <v>39.1</v>
       </c>
       <c r="G44" t="n">
-        <v>120.32</v>
+        <v>39.51</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.993</v>
       </c>
       <c r="I44" t="n">
-        <v>-2.159</v>
+        <v>-1.369</v>
       </c>
       <c r="J44" t="n">
-        <v>68.86</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>70.65000000000001</v>
+        <v>62.32</v>
       </c>
       <c r="L44" t="n">
-        <v>65.29000000000001</v>
+        <v>102.75</v>
       </c>
       <c r="M44" t="n">
-        <v>65.25</v>
+        <v>59.46</v>
       </c>
       <c r="N44" t="n">
-        <v>56.33</v>
+        <v>49.19</v>
       </c>
       <c r="O44" t="n">
-        <v>50.08</v>
+        <v>46.63</v>
       </c>
       <c r="P44" t="n">
-        <v>191.31</v>
+        <v>94.36</v>
       </c>
       <c r="Q44" t="n">
-        <v>169.33</v>
+        <v>121.87</v>
       </c>
       <c r="R44" t="n">
-        <v>1.13</v>
+        <v>0.77</v>
       </c>
       <c r="S44" t="n">
-        <v>126.18</v>
+        <v>40.1</v>
       </c>
       <c r="T44" t="n">
-        <v>127.17</v>
+        <v>40.26</v>
       </c>
       <c r="U44" t="n">
-        <v>125.14</v>
+        <v>39.67</v>
       </c>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
@@ -3674,69 +3674,69 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>688049</v>
+        <v>2074</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>炬芯科技</t>
+          <t>国轩高科</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>47.24</v>
+        <v>39.92</v>
       </c>
       <c r="D45" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="E45" t="n">
-        <v>46.48</v>
+        <v>37.74</v>
       </c>
       <c r="F45" t="n">
-        <v>45.37</v>
+        <v>36.24</v>
       </c>
       <c r="G45" t="n">
-        <v>45.68</v>
+        <v>36.73</v>
       </c>
       <c r="H45" t="n">
-        <v>-1.056</v>
+        <v>0.074</v>
       </c>
       <c r="I45" t="n">
-        <v>-1.598</v>
+        <v>-0.402</v>
       </c>
       <c r="J45" t="n">
-        <v>74.48999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>60.82</v>
+        <v>55.96</v>
       </c>
       <c r="L45" t="n">
-        <v>101.85</v>
+        <v>122.37</v>
       </c>
       <c r="M45" t="n">
-        <v>64.44</v>
+        <v>78.19</v>
       </c>
       <c r="N45" t="n">
-        <v>52.28</v>
+        <v>66.11</v>
       </c>
       <c r="O45" t="n">
-        <v>46.88</v>
+        <v>58.15</v>
       </c>
       <c r="P45" t="n">
-        <v>440.49</v>
+        <v>8999.74</v>
       </c>
       <c r="Q45" t="n">
-        <v>446.16</v>
+        <v>4899.07</v>
       </c>
       <c r="R45" t="n">
-        <v>0.99</v>
+        <v>1.84</v>
       </c>
       <c r="S45" t="n">
-        <v>47.45</v>
+        <v>39.29</v>
       </c>
       <c r="T45" t="n">
-        <v>47.7</v>
+        <v>39.99</v>
       </c>
       <c r="U45" t="n">
-        <v>46.72</v>
+        <v>38.92</v>
       </c>
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
@@ -3747,69 +3747,69 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>601689</v>
+        <v>300450</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>拓普集团</t>
+          <t>先导智能</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>60.04</v>
+        <v>54.18</v>
       </c>
       <c r="D46" t="n">
-        <v>0.92</v>
+        <v>1.82</v>
       </c>
       <c r="E46" t="n">
-        <v>59.57</v>
+        <v>52.18</v>
       </c>
       <c r="F46" t="n">
-        <v>58.59</v>
+        <v>49.81</v>
       </c>
       <c r="G46" t="n">
-        <v>58.6</v>
+        <v>49.23</v>
       </c>
       <c r="H46" t="n">
-        <v>-1.482</v>
+        <v>0.077</v>
       </c>
       <c r="I46" t="n">
-        <v>-2.181</v>
+        <v>-0.8169999999999999</v>
       </c>
       <c r="J46" t="n">
-        <v>65.95999999999999</v>
+        <v>86.44</v>
       </c>
       <c r="K46" t="n">
-        <v>58.33</v>
+        <v>72.52</v>
       </c>
       <c r="L46" t="n">
-        <v>81.20999999999999</v>
+        <v>114.3</v>
       </c>
       <c r="M46" t="n">
-        <v>58.24</v>
+        <v>77.67</v>
       </c>
       <c r="N46" t="n">
-        <v>49.55</v>
+        <v>64.7</v>
       </c>
       <c r="O46" t="n">
-        <v>43.78</v>
+        <v>55.77</v>
       </c>
       <c r="P46" t="n">
-        <v>2758.99</v>
+        <v>5976.97</v>
       </c>
       <c r="Q46" t="n">
-        <v>2472.04</v>
+        <v>4717.04</v>
       </c>
       <c r="R46" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
       <c r="S46" t="n">
-        <v>60.22</v>
+        <v>53.5</v>
       </c>
       <c r="T46" t="n">
-        <v>60.72</v>
+        <v>54.22</v>
       </c>
       <c r="U46" t="n">
-        <v>59.22</v>
+        <v>52.75</v>
       </c>
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
@@ -3820,69 +3820,69 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2050</v>
+        <v>603200</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>三花智控</t>
+          <t>上海洗霸</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>45.54</v>
+        <v>63.5</v>
       </c>
       <c r="D47" t="n">
-        <v>2.45</v>
+        <v>1.93</v>
       </c>
       <c r="E47" t="n">
-        <v>44.58</v>
+        <v>60.32</v>
       </c>
       <c r="F47" t="n">
-        <v>43.55</v>
+        <v>58.72</v>
       </c>
       <c r="G47" t="n">
-        <v>43.82</v>
+        <v>59.32</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.9379999999999999</v>
+        <v>-2.618</v>
       </c>
       <c r="I47" t="n">
-        <v>-1.446</v>
+        <v>-3.879</v>
       </c>
       <c r="J47" t="n">
-        <v>74.66</v>
+        <v>72.67</v>
       </c>
       <c r="K47" t="n">
-        <v>61.66</v>
+        <v>53.59</v>
       </c>
       <c r="L47" t="n">
-        <v>100.66</v>
+        <v>110.81</v>
       </c>
       <c r="M47" t="n">
-        <v>66.41</v>
+        <v>69.92</v>
       </c>
       <c r="N47" t="n">
-        <v>53.95</v>
+        <v>54.3</v>
       </c>
       <c r="O47" t="n">
-        <v>47.87</v>
+        <v>45.8</v>
       </c>
       <c r="P47" t="n">
-        <v>9022.459999999999</v>
+        <v>1314.65</v>
       </c>
       <c r="Q47" t="n">
-        <v>7243.94</v>
+        <v>647.77</v>
       </c>
       <c r="R47" t="n">
-        <v>1.25</v>
+        <v>2.03</v>
       </c>
       <c r="S47" t="n">
-        <v>44.8</v>
+        <v>62</v>
       </c>
       <c r="T47" t="n">
-        <v>45.8</v>
+        <v>64.28</v>
       </c>
       <c r="U47" t="n">
-        <v>44.56</v>
+        <v>61.9</v>
       </c>
       <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
@@ -3893,69 +3893,69 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>887</v>
+        <v>300409</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>中鼎股份</t>
+          <t>道氏技术</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>18.82</v>
+        <v>28.22</v>
       </c>
       <c r="D48" t="n">
-        <v>1.29</v>
+        <v>4.83</v>
       </c>
       <c r="E48" t="n">
-        <v>18.55</v>
+        <v>26.65</v>
       </c>
       <c r="F48" t="n">
-        <v>18.2</v>
+        <v>25.57</v>
       </c>
       <c r="G48" t="n">
-        <v>18.24</v>
+        <v>25.59</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.376</v>
+        <v>-0.3</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.577</v>
+        <v>-0.736</v>
       </c>
       <c r="J48" t="n">
-        <v>79.54000000000001</v>
+        <v>84.81999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>67.37</v>
+        <v>68.16</v>
       </c>
       <c r="L48" t="n">
-        <v>103.9</v>
+        <v>118.14</v>
       </c>
       <c r="M48" t="n">
-        <v>64.76000000000001</v>
+        <v>79.31999999999999</v>
       </c>
       <c r="N48" t="n">
-        <v>52.59</v>
+        <v>63.02</v>
       </c>
       <c r="O48" t="n">
-        <v>45.34</v>
+        <v>54.73</v>
       </c>
       <c r="P48" t="n">
-        <v>1356.04</v>
+        <v>4846.03</v>
       </c>
       <c r="Q48" t="n">
-        <v>1649.81</v>
+        <v>2979.26</v>
       </c>
       <c r="R48" t="n">
-        <v>0.82</v>
+        <v>1.63</v>
       </c>
       <c r="S48" t="n">
-        <v>18.82</v>
+        <v>27.37</v>
       </c>
       <c r="T48" t="n">
-        <v>18.92</v>
+        <v>28.22</v>
       </c>
       <c r="U48" t="n">
-        <v>18.61</v>
+        <v>26.98</v>
       </c>
       <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
@@ -3966,69 +3966,69 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>603236</v>
+        <v>2202</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>移远通信</t>
+          <t>金风科技</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>77.95</v>
+        <v>25.3</v>
       </c>
       <c r="D49" t="n">
-        <v>2.42</v>
+        <v>4.81</v>
       </c>
       <c r="E49" t="n">
-        <v>76.72</v>
+        <v>24.24</v>
       </c>
       <c r="F49" t="n">
-        <v>75.09</v>
+        <v>24.4</v>
       </c>
       <c r="G49" t="n">
-        <v>75.06</v>
+        <v>26.46</v>
       </c>
       <c r="H49" t="n">
-        <v>-1.406</v>
+        <v>-1.039</v>
       </c>
       <c r="I49" t="n">
-        <v>-2.341</v>
+        <v>-0.801</v>
       </c>
       <c r="J49" t="n">
-        <v>77.33</v>
+        <v>35.18</v>
       </c>
       <c r="K49" t="n">
-        <v>66.62</v>
+        <v>22.39</v>
       </c>
       <c r="L49" t="n">
-        <v>98.77</v>
+        <v>60.75</v>
       </c>
       <c r="M49" t="n">
-        <v>65.19</v>
+        <v>54.65</v>
       </c>
       <c r="N49" t="n">
-        <v>54.19</v>
+        <v>45.78</v>
       </c>
       <c r="O49" t="n">
-        <v>46.22</v>
+        <v>47.59</v>
       </c>
       <c r="P49" t="n">
-        <v>612.88</v>
+        <v>27970.37</v>
       </c>
       <c r="Q49" t="n">
-        <v>510.12</v>
+        <v>24078.93</v>
       </c>
       <c r="R49" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="S49" t="n">
-        <v>76.90000000000001</v>
+        <v>24.35</v>
       </c>
       <c r="T49" t="n">
-        <v>78.38</v>
+        <v>25.34</v>
       </c>
       <c r="U49" t="n">
-        <v>76.88</v>
+        <v>24.1</v>
       </c>
       <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
@@ -4039,69 +4039,69 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>603072</v>
+        <v>600990</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>天和磁材</t>
+          <t>四创电子</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>37.17</v>
+        <v>23.92</v>
       </c>
       <c r="D50" t="n">
-        <v>0.54</v>
+        <v>0.89</v>
       </c>
       <c r="E50" t="n">
-        <v>36.83</v>
+        <v>23.29</v>
       </c>
       <c r="F50" t="n">
-        <v>36.3</v>
+        <v>22.76</v>
       </c>
       <c r="G50" t="n">
-        <v>36.45</v>
+        <v>22.98</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.959</v>
+        <v>-0.665</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.321</v>
+        <v>-0.989</v>
       </c>
       <c r="J50" t="n">
-        <v>72.93000000000001</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>67.41</v>
+        <v>58.4</v>
       </c>
       <c r="L50" t="n">
-        <v>83.98</v>
+        <v>113.49</v>
       </c>
       <c r="M50" t="n">
-        <v>62.46</v>
+        <v>71.12</v>
       </c>
       <c r="N50" t="n">
-        <v>48.28</v>
+        <v>53.55</v>
       </c>
       <c r="O50" t="n">
-        <v>44.05</v>
+        <v>44.9</v>
       </c>
       <c r="P50" t="n">
-        <v>226.91</v>
+        <v>555.39</v>
       </c>
       <c r="Q50" t="n">
-        <v>226.37</v>
+        <v>443.15</v>
       </c>
       <c r="R50" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="S50" t="n">
-        <v>37.3</v>
+        <v>23.72</v>
       </c>
       <c r="T50" t="n">
-        <v>37.3</v>
+        <v>24.15</v>
       </c>
       <c r="U50" t="n">
-        <v>36.81</v>
+        <v>23.32</v>
       </c>
       <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
@@ -4112,69 +4112,69 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>301023</v>
+        <v>2025</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>奕帆传动</t>
+          <t>航天电器</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>40.22</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>1.11</v>
+        <v>1.71</v>
       </c>
       <c r="E51" t="n">
-        <v>39.96</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="F51" t="n">
-        <v>39.1</v>
+        <v>69.78</v>
       </c>
       <c r="G51" t="n">
-        <v>39.51</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.993</v>
+        <v>5.26</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.369</v>
+        <v>3.909</v>
       </c>
       <c r="J51" t="n">
-        <v>75.79000000000001</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>62.32</v>
+        <v>77.45</v>
       </c>
       <c r="L51" t="n">
-        <v>102.75</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M51" t="n">
-        <v>59.46</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="N51" t="n">
-        <v>49.19</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="O51" t="n">
-        <v>46.63</v>
+        <v>65.87</v>
       </c>
       <c r="P51" t="n">
-        <v>94.36</v>
+        <v>3692.27</v>
       </c>
       <c r="Q51" t="n">
-        <v>121.87</v>
+        <v>3484.87</v>
       </c>
       <c r="R51" t="n">
-        <v>0.77</v>
+        <v>1.06</v>
       </c>
       <c r="S51" t="n">
-        <v>40.1</v>
+        <v>77</v>
       </c>
       <c r="T51" t="n">
-        <v>40.26</v>
+        <v>81.75</v>
       </c>
       <c r="U51" t="n">
-        <v>39.67</v>
+        <v>75.22</v>
       </c>
       <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
@@ -4185,69 +4185,69 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2074</v>
+        <v>600584</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>国轩高科</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>39.92</v>
+        <v>44.34</v>
       </c>
       <c r="D52" t="n">
-        <v>1.06</v>
+        <v>3.48</v>
       </c>
       <c r="E52" t="n">
-        <v>37.74</v>
+        <v>42.82</v>
       </c>
       <c r="F52" t="n">
-        <v>36.24</v>
+        <v>40.79</v>
       </c>
       <c r="G52" t="n">
-        <v>36.73</v>
+        <v>41.08</v>
       </c>
       <c r="H52" t="n">
-        <v>0.074</v>
+        <v>-0.536</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.402</v>
+        <v>-1.197</v>
       </c>
       <c r="J52" t="n">
-        <v>78.09999999999999</v>
+        <v>78.52</v>
       </c>
       <c r="K52" t="n">
-        <v>55.96</v>
+        <v>62.88</v>
       </c>
       <c r="L52" t="n">
-        <v>122.37</v>
+        <v>109.8</v>
       </c>
       <c r="M52" t="n">
-        <v>78.19</v>
+        <v>76.41</v>
       </c>
       <c r="N52" t="n">
-        <v>66.11</v>
+        <v>59.95</v>
       </c>
       <c r="O52" t="n">
-        <v>58.15</v>
+        <v>53.33</v>
       </c>
       <c r="P52" t="n">
-        <v>8999.74</v>
+        <v>8255</v>
       </c>
       <c r="Q52" t="n">
-        <v>4899.07</v>
+        <v>5168.2</v>
       </c>
       <c r="R52" t="n">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="S52" t="n">
-        <v>39.29</v>
+        <v>43.6</v>
       </c>
       <c r="T52" t="n">
-        <v>39.99</v>
+        <v>45.08</v>
       </c>
       <c r="U52" t="n">
-        <v>38.92</v>
+        <v>43.3</v>
       </c>
       <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
@@ -4258,69 +4258,69 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>300450</v>
+        <v>300759</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>先导智能</t>
+          <t>康龙化成</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>54.18</v>
+        <v>31.38</v>
       </c>
       <c r="D53" t="n">
-        <v>1.82</v>
+        <v>2.31</v>
       </c>
       <c r="E53" t="n">
-        <v>52.18</v>
+        <v>30.82</v>
       </c>
       <c r="F53" t="n">
-        <v>49.81</v>
+        <v>30.33</v>
       </c>
       <c r="G53" t="n">
-        <v>49.23</v>
+        <v>28.37</v>
       </c>
       <c r="H53" t="n">
-        <v>0.077</v>
+        <v>0.802</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.8169999999999999</v>
+        <v>0.358</v>
       </c>
       <c r="J53" t="n">
-        <v>86.44</v>
+        <v>79.27</v>
       </c>
       <c r="K53" t="n">
-        <v>72.52</v>
+        <v>78.41</v>
       </c>
       <c r="L53" t="n">
-        <v>114.3</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="M53" t="n">
-        <v>77.67</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>64.7</v>
+        <v>68.05</v>
       </c>
       <c r="O53" t="n">
-        <v>55.77</v>
+        <v>60.09</v>
       </c>
       <c r="P53" t="n">
-        <v>5976.97</v>
+        <v>3502.51</v>
       </c>
       <c r="Q53" t="n">
-        <v>4717.04</v>
+        <v>3481.18</v>
       </c>
       <c r="R53" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="S53" t="n">
-        <v>53.5</v>
+        <v>30.78</v>
       </c>
       <c r="T53" t="n">
-        <v>54.22</v>
+        <v>31.38</v>
       </c>
       <c r="U53" t="n">
-        <v>52.75</v>
+        <v>30.36</v>
       </c>
       <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
@@ -4331,69 +4331,69 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>688778</v>
+        <v>301333</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>厦钨新能</t>
+          <t>诺思格</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>75.43000000000001</v>
+        <v>68.47</v>
       </c>
       <c r="D54" t="n">
-        <v>1.89</v>
+        <v>3.38</v>
       </c>
       <c r="E54" t="n">
-        <v>74.29000000000001</v>
+        <v>67.53</v>
       </c>
       <c r="F54" t="n">
-        <v>72.59</v>
+        <v>67.92</v>
       </c>
       <c r="G54" t="n">
-        <v>72.73</v>
+        <v>63.7</v>
       </c>
       <c r="H54" t="n">
-        <v>-1.106</v>
+        <v>0.39</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.851</v>
+        <v>-0.33</v>
       </c>
       <c r="J54" t="n">
-        <v>63.5</v>
+        <v>51.08</v>
       </c>
       <c r="K54" t="n">
+        <v>56.11</v>
+      </c>
+      <c r="L54" t="n">
+        <v>41.02</v>
+      </c>
+      <c r="M54" t="n">
+        <v>61.04</v>
+      </c>
+      <c r="N54" t="n">
         <v>56.19</v>
       </c>
-      <c r="L54" t="n">
-        <v>78.14</v>
-      </c>
-      <c r="M54" t="n">
-        <v>59.64</v>
-      </c>
-      <c r="N54" t="n">
-        <v>52.83</v>
-      </c>
       <c r="O54" t="n">
-        <v>48.94</v>
+        <v>52.61</v>
       </c>
       <c r="P54" t="n">
-        <v>753.52</v>
+        <v>197.29</v>
       </c>
       <c r="Q54" t="n">
-        <v>519.66</v>
+        <v>258.68</v>
       </c>
       <c r="R54" t="n">
-        <v>1.45</v>
+        <v>0.76</v>
       </c>
       <c r="S54" t="n">
-        <v>74.23</v>
+        <v>67</v>
       </c>
       <c r="T54" t="n">
-        <v>75.8</v>
+        <v>68.47</v>
       </c>
       <c r="U54" t="n">
-        <v>72.34</v>
+        <v>66.19</v>
       </c>
       <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
@@ -4404,69 +4404,69 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>688116</v>
+        <v>963</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>天奈科技</t>
+          <t>华东医药</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>41.26</v>
+        <v>35</v>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="E55" t="n">
-        <v>40.09</v>
+        <v>35.64</v>
       </c>
       <c r="F55" t="n">
-        <v>39.27</v>
+        <v>35.89</v>
       </c>
       <c r="G55" t="n">
-        <v>40.18</v>
+        <v>35.39</v>
       </c>
       <c r="H55" t="n">
-        <v>-1.023</v>
+        <v>0.008</v>
       </c>
       <c r="I55" t="n">
-        <v>-1.377</v>
+        <v>-0.008</v>
       </c>
       <c r="J55" t="n">
-        <v>71.59999999999999</v>
+        <v>36.01</v>
       </c>
       <c r="K55" t="n">
-        <v>53.07</v>
+        <v>52.55</v>
       </c>
       <c r="L55" t="n">
-        <v>108.66</v>
+        <v>2.95</v>
       </c>
       <c r="M55" t="n">
-        <v>64.81999999999999</v>
+        <v>37.99</v>
       </c>
       <c r="N55" t="n">
-        <v>52.66</v>
+        <v>45.22</v>
       </c>
       <c r="O55" t="n">
-        <v>46.62</v>
+        <v>45.59</v>
       </c>
       <c r="P55" t="n">
-        <v>632.09</v>
+        <v>995.91</v>
       </c>
       <c r="Q55" t="n">
-        <v>724.55</v>
+        <v>1154.09</v>
       </c>
       <c r="R55" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="S55" t="n">
-        <v>40.48</v>
+        <v>35.01</v>
       </c>
       <c r="T55" t="n">
-        <v>41.41</v>
+        <v>35.1</v>
       </c>
       <c r="U55" t="n">
-        <v>40.47</v>
+        <v>34.37</v>
       </c>
       <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr">
@@ -4477,69 +4477,69 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>603200</v>
+        <v>603658</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>上海洗霸</t>
+          <t>安图生物</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>63.5</v>
+        <v>34.17</v>
       </c>
       <c r="D56" t="n">
-        <v>1.93</v>
+        <v>1.03</v>
       </c>
       <c r="E56" t="n">
-        <v>60.32</v>
+        <v>34.38</v>
       </c>
       <c r="F56" t="n">
-        <v>58.72</v>
+        <v>34.28</v>
       </c>
       <c r="G56" t="n">
-        <v>59.32</v>
+        <v>34.01</v>
       </c>
       <c r="H56" t="n">
-        <v>-2.618</v>
+        <v>-0.215</v>
       </c>
       <c r="I56" t="n">
-        <v>-3.879</v>
+        <v>-0.34</v>
       </c>
       <c r="J56" t="n">
-        <v>72.67</v>
+        <v>55.83</v>
       </c>
       <c r="K56" t="n">
-        <v>53.59</v>
+        <v>64.28</v>
       </c>
       <c r="L56" t="n">
-        <v>110.81</v>
+        <v>38.92</v>
       </c>
       <c r="M56" t="n">
-        <v>69.92</v>
+        <v>49.31</v>
       </c>
       <c r="N56" t="n">
-        <v>54.3</v>
+        <v>47.97</v>
       </c>
       <c r="O56" t="n">
-        <v>45.8</v>
+        <v>45.75</v>
       </c>
       <c r="P56" t="n">
-        <v>1314.65</v>
+        <v>158.72</v>
       </c>
       <c r="Q56" t="n">
-        <v>647.77</v>
+        <v>201.9</v>
       </c>
       <c r="R56" t="n">
-        <v>2.03</v>
+        <v>0.79</v>
       </c>
       <c r="S56" t="n">
-        <v>62</v>
+        <v>34.01</v>
       </c>
       <c r="T56" t="n">
-        <v>64.28</v>
+        <v>34.2</v>
       </c>
       <c r="U56" t="n">
-        <v>61.9</v>
+        <v>33.68</v>
       </c>
       <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
@@ -4550,1021 +4550,72 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>300409</v>
+        <v>300357</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>道氏技术</t>
+          <t>我武生物</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>28.22</v>
+        <v>26.36</v>
       </c>
       <c r="D57" t="n">
-        <v>4.83</v>
+        <v>0.38</v>
       </c>
       <c r="E57" t="n">
-        <v>26.65</v>
+        <v>26.21</v>
       </c>
       <c r="F57" t="n">
-        <v>25.57</v>
+        <v>26.08</v>
       </c>
       <c r="G57" t="n">
-        <v>25.59</v>
+        <v>25.45</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.3</v>
+        <v>0.092</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.736</v>
+        <v>-0.12</v>
       </c>
       <c r="J57" t="n">
-        <v>84.81999999999999</v>
+        <v>68.31</v>
       </c>
       <c r="K57" t="n">
-        <v>68.16</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>118.14</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="M57" t="n">
-        <v>79.31999999999999</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="N57" t="n">
-        <v>63.02</v>
+        <v>57.39</v>
       </c>
       <c r="O57" t="n">
-        <v>54.73</v>
+        <v>50.44</v>
       </c>
       <c r="P57" t="n">
-        <v>4846.03</v>
+        <v>1182.39</v>
       </c>
       <c r="Q57" t="n">
-        <v>2979.26</v>
+        <v>1230.97</v>
       </c>
       <c r="R57" t="n">
-        <v>1.63</v>
+        <v>0.96</v>
       </c>
       <c r="S57" t="n">
-        <v>27.37</v>
+        <v>26.32</v>
       </c>
       <c r="T57" t="n">
-        <v>28.22</v>
+        <v>26.4</v>
       </c>
       <c r="U57" t="n">
-        <v>26.98</v>
+        <v>25.62</v>
       </c>
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>2202</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>金风科技</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="D58" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="E58" t="n">
-        <v>24.24</v>
-      </c>
-      <c r="F58" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="G58" t="n">
-        <v>26.46</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-1.039</v>
-      </c>
-      <c r="I58" t="n">
-        <v>-0.801</v>
-      </c>
-      <c r="J58" t="n">
-        <v>35.18</v>
-      </c>
-      <c r="K58" t="n">
-        <v>22.39</v>
-      </c>
-      <c r="L58" t="n">
-        <v>60.75</v>
-      </c>
-      <c r="M58" t="n">
-        <v>54.65</v>
-      </c>
-      <c r="N58" t="n">
-        <v>45.78</v>
-      </c>
-      <c r="O58" t="n">
-        <v>47.59</v>
-      </c>
-      <c r="P58" t="n">
-        <v>27970.37</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>24078.93</v>
-      </c>
-      <c r="R58" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S58" t="n">
-        <v>24.35</v>
-      </c>
-      <c r="T58" t="n">
-        <v>25.34</v>
-      </c>
-      <c r="U58" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>688066</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>航天宏图</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>19.64</v>
-      </c>
-      <c r="D59" t="n">
-        <v>7.09</v>
-      </c>
-      <c r="E59" t="n">
-        <v>18.83</v>
-      </c>
-      <c r="F59" t="n">
-        <v>18.46</v>
-      </c>
-      <c r="G59" t="n">
-        <v>19.74</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-1.61</v>
-      </c>
-      <c r="I59" t="n">
-        <v>-1.903</v>
-      </c>
-      <c r="J59" t="n">
-        <v>56.44</v>
-      </c>
-      <c r="K59" t="n">
-        <v>39.76</v>
-      </c>
-      <c r="L59" t="n">
-        <v>89.81999999999999</v>
-      </c>
-      <c r="M59" t="n">
-        <v>59.04</v>
-      </c>
-      <c r="N59" t="n">
-        <v>46.13</v>
-      </c>
-      <c r="O59" t="n">
-        <v>41.93</v>
-      </c>
-      <c r="P59" t="n">
-        <v>1554.03</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>1085.47</v>
-      </c>
-      <c r="R59" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S59" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="T59" t="n">
-        <v>19.96</v>
-      </c>
-      <c r="U59" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>600990</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>四创电子</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>23.92</v>
-      </c>
-      <c r="D60" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E60" t="n">
-        <v>23.29</v>
-      </c>
-      <c r="F60" t="n">
-        <v>22.76</v>
-      </c>
-      <c r="G60" t="n">
-        <v>22.98</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-0.665</v>
-      </c>
-      <c r="I60" t="n">
-        <v>-0.989</v>
-      </c>
-      <c r="J60" t="n">
-        <v>76.76000000000001</v>
-      </c>
-      <c r="K60" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="L60" t="n">
-        <v>113.49</v>
-      </c>
-      <c r="M60" t="n">
-        <v>71.12</v>
-      </c>
-      <c r="N60" t="n">
-        <v>53.55</v>
-      </c>
-      <c r="O60" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="P60" t="n">
-        <v>555.39</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>443.15</v>
-      </c>
-      <c r="R60" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S60" t="n">
-        <v>23.72</v>
-      </c>
-      <c r="T60" t="n">
-        <v>24.15</v>
-      </c>
-      <c r="U60" t="n">
-        <v>23.32</v>
-      </c>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>航天电器</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>78.68000000000001</v>
-      </c>
-      <c r="D61" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="E61" t="n">
-        <v>76.31999999999999</v>
-      </c>
-      <c r="F61" t="n">
-        <v>69.78</v>
-      </c>
-      <c r="G61" t="n">
-        <v>66.26000000000001</v>
-      </c>
-      <c r="H61" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="I61" t="n">
-        <v>3.909</v>
-      </c>
-      <c r="J61" t="n">
-        <v>83.76000000000001</v>
-      </c>
-      <c r="K61" t="n">
-        <v>77.45</v>
-      </c>
-      <c r="L61" t="n">
-        <v>96.40000000000001</v>
-      </c>
-      <c r="M61" t="n">
-        <v>75.76000000000001</v>
-      </c>
-      <c r="N61" t="n">
-        <v>70.23999999999999</v>
-      </c>
-      <c r="O61" t="n">
-        <v>65.87</v>
-      </c>
-      <c r="P61" t="n">
-        <v>3692.27</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>3484.87</v>
-      </c>
-      <c r="R61" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="S61" t="n">
-        <v>77</v>
-      </c>
-      <c r="T61" t="n">
-        <v>81.75</v>
-      </c>
-      <c r="U61" t="n">
-        <v>75.22</v>
-      </c>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>600584</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>长电科技</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>44.34</v>
-      </c>
-      <c r="D62" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="E62" t="n">
-        <v>42.82</v>
-      </c>
-      <c r="F62" t="n">
-        <v>40.79</v>
-      </c>
-      <c r="G62" t="n">
-        <v>41.08</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-0.536</v>
-      </c>
-      <c r="I62" t="n">
-        <v>-1.197</v>
-      </c>
-      <c r="J62" t="n">
-        <v>78.52</v>
-      </c>
-      <c r="K62" t="n">
-        <v>62.88</v>
-      </c>
-      <c r="L62" t="n">
-        <v>109.8</v>
-      </c>
-      <c r="M62" t="n">
-        <v>76.41</v>
-      </c>
-      <c r="N62" t="n">
-        <v>59.95</v>
-      </c>
-      <c r="O62" t="n">
-        <v>53.33</v>
-      </c>
-      <c r="P62" t="n">
-        <v>8255</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>5168.2</v>
-      </c>
-      <c r="R62" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="S62" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="T62" t="n">
-        <v>45.08</v>
-      </c>
-      <c r="U62" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>688295</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>中复神鹰</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>52.98</v>
-      </c>
-      <c r="D63" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="E63" t="n">
-        <v>51.56</v>
-      </c>
-      <c r="F63" t="n">
-        <v>51.79</v>
-      </c>
-      <c r="G63" t="n">
-        <v>55.42</v>
-      </c>
-      <c r="H63" t="n">
-        <v>2.422</v>
-      </c>
-      <c r="I63" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="J63" t="n">
-        <v>32.32</v>
-      </c>
-      <c r="K63" t="n">
-        <v>24.85</v>
-      </c>
-      <c r="L63" t="n">
-        <v>47.26</v>
-      </c>
-      <c r="M63" t="n">
-        <v>53.96</v>
-      </c>
-      <c r="N63" t="n">
-        <v>55.45</v>
-      </c>
-      <c r="O63" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="P63" t="n">
-        <v>2128.57</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>2545.26</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="S63" t="n">
-        <v>52</v>
-      </c>
-      <c r="T63" t="n">
-        <v>54.56</v>
-      </c>
-      <c r="U63" t="n">
-        <v>51.82</v>
-      </c>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>300759</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>康龙化成</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>31.38</v>
-      </c>
-      <c r="D64" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="E64" t="n">
-        <v>30.82</v>
-      </c>
-      <c r="F64" t="n">
-        <v>30.33</v>
-      </c>
-      <c r="G64" t="n">
-        <v>28.37</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.802</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0.358</v>
-      </c>
-      <c r="J64" t="n">
-        <v>79.27</v>
-      </c>
-      <c r="K64" t="n">
-        <v>78.41</v>
-      </c>
-      <c r="L64" t="n">
-        <v>80.98999999999999</v>
-      </c>
-      <c r="M64" t="n">
-        <v>75.70999999999999</v>
-      </c>
-      <c r="N64" t="n">
-        <v>68.05</v>
-      </c>
-      <c r="O64" t="n">
-        <v>60.09</v>
-      </c>
-      <c r="P64" t="n">
-        <v>3502.51</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>3481.18</v>
-      </c>
-      <c r="R64" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="S64" t="n">
-        <v>30.78</v>
-      </c>
-      <c r="T64" t="n">
-        <v>31.38</v>
-      </c>
-      <c r="U64" t="n">
-        <v>30.36</v>
-      </c>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>688621</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>阳光诺和</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="D65" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E65" t="n">
-        <v>66.84999999999999</v>
-      </c>
-      <c r="F65" t="n">
-        <v>66.78</v>
-      </c>
-      <c r="G65" t="n">
-        <v>64.19</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="J65" t="n">
-        <v>52.55</v>
-      </c>
-      <c r="K65" t="n">
-        <v>60.59</v>
-      </c>
-      <c r="L65" t="n">
-        <v>36.46</v>
-      </c>
-      <c r="M65" t="n">
-        <v>58.47</v>
-      </c>
-      <c r="N65" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="O65" t="n">
-        <v>52.75</v>
-      </c>
-      <c r="P65" t="n">
-        <v>257.42</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>247.15</v>
-      </c>
-      <c r="R65" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="S65" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="T65" t="n">
-        <v>67.48</v>
-      </c>
-      <c r="U65" t="n">
-        <v>64.31</v>
-      </c>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>301333</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>诺思格</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>68.47</v>
-      </c>
-      <c r="D66" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="E66" t="n">
-        <v>67.53</v>
-      </c>
-      <c r="F66" t="n">
-        <v>67.92</v>
-      </c>
-      <c r="G66" t="n">
-        <v>63.7</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="I66" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="J66" t="n">
-        <v>51.08</v>
-      </c>
-      <c r="K66" t="n">
-        <v>56.11</v>
-      </c>
-      <c r="L66" t="n">
-        <v>41.02</v>
-      </c>
-      <c r="M66" t="n">
-        <v>61.04</v>
-      </c>
-      <c r="N66" t="n">
-        <v>56.19</v>
-      </c>
-      <c r="O66" t="n">
-        <v>52.61</v>
-      </c>
-      <c r="P66" t="n">
-        <v>197.29</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>258.68</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="S66" t="n">
-        <v>67</v>
-      </c>
-      <c r="T66" t="n">
-        <v>68.47</v>
-      </c>
-      <c r="U66" t="n">
-        <v>66.19</v>
-      </c>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>963</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>华东医药</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>35</v>
-      </c>
-      <c r="D67" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E67" t="n">
-        <v>35.64</v>
-      </c>
-      <c r="F67" t="n">
-        <v>35.89</v>
-      </c>
-      <c r="G67" t="n">
-        <v>35.39</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="I67" t="n">
-        <v>-0.008</v>
-      </c>
-      <c r="J67" t="n">
-        <v>36.01</v>
-      </c>
-      <c r="K67" t="n">
-        <v>52.55</v>
-      </c>
-      <c r="L67" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="M67" t="n">
-        <v>37.99</v>
-      </c>
-      <c r="N67" t="n">
-        <v>45.22</v>
-      </c>
-      <c r="O67" t="n">
-        <v>45.59</v>
-      </c>
-      <c r="P67" t="n">
-        <v>995.91</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>1154.09</v>
-      </c>
-      <c r="R67" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="S67" t="n">
-        <v>35.01</v>
-      </c>
-      <c r="T67" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="U67" t="n">
-        <v>34.37</v>
-      </c>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>603658</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>安图生物</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>34.17</v>
-      </c>
-      <c r="D68" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E68" t="n">
-        <v>34.38</v>
-      </c>
-      <c r="F68" t="n">
-        <v>34.28</v>
-      </c>
-      <c r="G68" t="n">
-        <v>34.01</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-0.215</v>
-      </c>
-      <c r="I68" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="J68" t="n">
-        <v>55.83</v>
-      </c>
-      <c r="K68" t="n">
-        <v>64.28</v>
-      </c>
-      <c r="L68" t="n">
-        <v>38.92</v>
-      </c>
-      <c r="M68" t="n">
-        <v>49.31</v>
-      </c>
-      <c r="N68" t="n">
-        <v>47.97</v>
-      </c>
-      <c r="O68" t="n">
-        <v>45.75</v>
-      </c>
-      <c r="P68" t="n">
-        <v>158.72</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>201.9</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="S68" t="n">
-        <v>34.01</v>
-      </c>
-      <c r="T68" t="n">
-        <v>34.2</v>
-      </c>
-      <c r="U68" t="n">
-        <v>33.68</v>
-      </c>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>300357</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>我武生物</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>26.36</v>
-      </c>
-      <c r="D69" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E69" t="n">
-        <v>26.21</v>
-      </c>
-      <c r="F69" t="n">
-        <v>26.08</v>
-      </c>
-      <c r="G69" t="n">
-        <v>25.45</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="I69" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="J69" t="n">
-        <v>68.31</v>
-      </c>
-      <c r="K69" t="n">
-        <v>69.79000000000001</v>
-      </c>
-      <c r="L69" t="n">
-        <v>65.34999999999999</v>
-      </c>
-      <c r="M69" t="n">
-        <v>65.98999999999999</v>
-      </c>
-      <c r="N69" t="n">
-        <v>57.39</v>
-      </c>
-      <c r="O69" t="n">
-        <v>50.44</v>
-      </c>
-      <c r="P69" t="n">
-        <v>1182.39</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>1230.97</v>
-      </c>
-      <c r="R69" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="S69" t="n">
-        <v>26.32</v>
-      </c>
-      <c r="T69" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="U69" t="n">
-        <v>25.62</v>
-      </c>
-      <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>688050</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>爱博医疗</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>51.18</v>
-      </c>
-      <c r="D70" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E70" t="n">
-        <v>51.47</v>
-      </c>
-      <c r="F70" t="n">
-        <v>51.56</v>
-      </c>
-      <c r="G70" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-1.397</v>
-      </c>
-      <c r="I70" t="n">
-        <v>-1.649</v>
-      </c>
-      <c r="J70" t="n">
-        <v>32.82</v>
-      </c>
-      <c r="K70" t="n">
-        <v>43.48</v>
-      </c>
-      <c r="L70" t="n">
-        <v>11.52</v>
-      </c>
-      <c r="M70" t="n">
-        <v>44.74</v>
-      </c>
-      <c r="N70" t="n">
-        <v>41.17</v>
-      </c>
-      <c r="O70" t="n">
-        <v>39</v>
-      </c>
-      <c r="P70" t="n">
-        <v>95.91</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>157.75</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="S70" t="n">
-        <v>51.01</v>
-      </c>
-      <c r="T70" t="n">
-        <v>51.26</v>
-      </c>
-      <c r="U70" t="n">
-        <v>50.81</v>
-      </c>
-      <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>
